--- a/source-artifacts/sharepoint/AccountClosure_SharePoint_List_Setup.xlsx
+++ b/source-artifacts/sharepoint/AccountClosure_SharePoint_List_Setup.xlsx
@@ -18,6 +18,7 @@
     <sheet name="8. Role_Mapping" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="9. System_Config" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10. Litigation_Register" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11. Task_Templates" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1414,13 +1415,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E7D44"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1439,21 +1441,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>New_Request   ·   คำขอปิดบัญชี (หัวเรื่อง 1 คำขอ = 1 แถว)</t>
+          <t>Task_Templates   ·   แม่แบบงาน Settlement (ต่อ product)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Type: List (extend existing)    ·    Header — one row per closure request. The single-value boxes on every screen live here.</t>
+          <t>Type: List (new · config)    ·    Config — the per-product settlement task chains (round-17). One row per (product, step). The Dispatch Settlement flow copies matching rows into Request_Tasks for the products the customer holds. Change a chain here, not in code.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>⚑ Indexed columns to add (List settings → Indexed columns): CurrentStage, RequestStatus, Title</t>
+          <t>⚑ Indexed columns to add (List settings → Indexed columns): —</t>
         </is>
       </c>
     </row>
@@ -1538,26 +1540,26 @@
           <t>Yes (primary)</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr"/>
       <c r="I6" s="14" t="inlineStr"/>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>เลขที่คำขอ (RequestID)</t>
+          <t>TemplateID</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>Auto-generated request reference, e.g. INVX888-1999.  •  Primary key; run number via Flow 1 + System_Config seed</t>
+          <t>Auto number / key.  •  Primary key</t>
         </is>
       </c>
     </row>
@@ -1567,6 +1569,414 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>TFEX, Offshore, Equity + Bond + SN, บัญชีซื้อขายหน่วยลงทุน, DA Digital Assets, LiVEx, Algo</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>The product chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>StepNo</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>StepNo</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>ลำดับขั้น</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>Execution order within the product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>OwnerDept</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>OwnerDept</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>CAM, Cash, EQ, Offshore, DA</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>ทีมเจ้าของงาน</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>Department that performs this step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>TaskName</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>TaskName</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Single line of text</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr"/>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>งานที่ต้องทำ</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>The task label shown in the queue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>IsOptional</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>IsOptional</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>ไม่บังคับ</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>Optional step (Offshore FCD, DA transfer-if-alive, post-interest).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>New_Request   ·   คำขอปิดบัญชี (หัวเรื่อง 1 คำขอ = 1 แถว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Type: List (extend existing)    ·    Header — one row per closure request. The single-value boxes on every screen live here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>⚑ Indexed columns to add (List settings → Indexed columns): CurrentStage, RequestStatus, Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Column display name</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Internal name</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>SharePoint type</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Enforce unique</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Indexed</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Choices (one per line in SP)</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>ชื่อไทย (TH label)</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Notes / description</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Single line of text</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Yes (primary)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr"/>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>เลขที่คำขอ (RequestID)</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>Auto-generated request reference, e.g. INVX888-1999.  •  Primary key; run number via Flow 1 + System_Config seed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
           <t>CustomerName</t>
         </is>
       </c>
@@ -3019,7 +3429,7 @@
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>Mutual-fund closing decision — pick exactly one.</t>
+          <t>Mutual-fund closing decision — pick exactly one (Middle-1 only, round-17).</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3439,17 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>RelinquishDA</t>
+          <t>MFSuspendAccounts</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>RelinquishDA</t>
+          <t>MFSuspendAccounts</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>Choice</t>
+          <t>Single line of text</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -3058,19 +3468,15 @@
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>ยินยอม (Consent), ไม่ยินยอม (Decline)</t>
-        </is>
-      </c>
+      <c r="I37" s="21" t="inlineStr"/>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>ประสงค์สละสินทรัพย์ DA</t>
+          <t>บัญชี Suspend (กองทุน)</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>Customer's intent to relinquish DA assets.</t>
+          <t>Fund accounts to Suspend when the unit-holder decision is option 2 or 3 (comma-separated).  •  Middle-1 mutual-fund decision; round-17</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3486,12 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>LitigationStatus</t>
+          <t>RelinquishDA</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>LitigationStatus</t>
+          <t>RelinquishDA</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -3111,17 +3517,17 @@
       <c r="H38" s="20" t="inlineStr"/>
       <c r="I38" s="21" t="inlineStr">
         <is>
-          <t>Pending, Clean, Found</t>
+          <t>ยินยอม (Consent), ไม่ยินยอม (Decline)</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>ผลตรวจการฟ้องร้อง</t>
+          <t>ประสงค์สละสินทรัพย์ DA</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>Auto litigation check result (written by Flow 2).</t>
+          <t>Customer's intent to relinquish DA assets.</t>
         </is>
       </c>
     </row>
@@ -3131,17 +3537,17 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>LitigationReason</t>
+          <t>LitigationStatus</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>LitigationReason</t>
+          <t>LitigationStatus</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>Multiple lines of text</t>
+          <t>Choice</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -3160,15 +3566,19 @@
         </is>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
-      <c r="I39" s="21" t="inlineStr"/>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>Pending, Clean, Found</t>
+        </is>
+      </c>
       <c r="J39" s="22" t="inlineStr">
         <is>
-          <t>สาเหตุการฟ้องร้อง</t>
+          <t>ผลตรวจการฟ้องร้อง</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>Reason behind the litigation (when Found).</t>
+          <t>Auto litigation check result (written by Flow 2).</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3588,12 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>AOOpinion</t>
+          <t>LitigationReason</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>AOOpinion</t>
+          <t>LitigationReason</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -3210,12 +3620,12 @@
       <c r="I40" s="21" t="inlineStr"/>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>ความเห็นเจ้าหน้าที่/บริษัท</t>
+          <t>สาเหตุการฟ้องร้อง</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>Marketing officer / company recommendation.  •  Sales-1 AO OPINION box</t>
+          <t>Reason behind the litigation (when Found).</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3635,12 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>AORemark</t>
+          <t>AOOpinion</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>AORemark</t>
+          <t>AOOpinion</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -3257,63 +3667,59 @@
       <c r="I41" s="21" t="inlineStr"/>
       <c r="J41" s="22" t="inlineStr">
         <is>
+          <t>ความเห็นเจ้าหน้าที่/บริษัท</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>Marketing officer / company recommendation.  •  Sales-1 AO OPINION box</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>AORemark</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>AORemark</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Multiple lines of text</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr"/>
+      <c r="I42" s="21" t="inlineStr"/>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
           <t>AO Remark</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="K42" s="23" t="inlineStr">
         <is>
           <t>Free-text remark from the AO.  •  Sales-1 AO REMARK box</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>RefundMethod</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>RefundMethod</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>Choice</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr"/>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>โอนเข้าบัญชีธนาคาร, เช็ค, อื่นๆ</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>วิธีคืนเงิน</t>
-        </is>
-      </c>
-      <c r="K42" s="16" t="inlineStr">
-        <is>
-          <t>How remaining money is refunded.</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3729,12 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankName</t>
+          <t>RefundMethod</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankName</t>
+          <t>RefundMethod</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -3354,17 +3760,17 @@
       <c r="H43" s="13" t="inlineStr"/>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>รายชื่อธนาคาร</t>
+          <t>โอนเข้าบัญชีธนาคาร, เช็ค, อื่นๆ</t>
         </is>
       </c>
       <c r="J43" s="15" t="inlineStr">
         <is>
-          <t>ธนาคารผู้รับ</t>
+          <t>วิธีคืนเงิน</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr">
         <is>
-          <t>Receiving bank.</t>
+          <t>How remaining money is refunded.</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3780,17 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankBranch</t>
+          <t>ReceivingBankName</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankBranch</t>
+          <t>ReceivingBankName</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Single line of text</t>
+          <t>Choice</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -3403,15 +3809,19 @@
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr"/>
-      <c r="I44" s="14" t="inlineStr"/>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>รายชื่อธนาคาร</t>
+        </is>
+      </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>สาขา</t>
+          <t>ธนาคารผู้รับ</t>
         </is>
       </c>
       <c r="K44" s="16" t="inlineStr">
         <is>
-          <t>Receiving bank branch.</t>
+          <t>Receiving bank.</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3831,12 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankAccountNumber</t>
+          <t>ReceivingBankBranch</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankAccountNumber</t>
+          <t>ReceivingBankBranch</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -3453,12 +3863,12 @@
       <c r="I45" s="14" t="inlineStr"/>
       <c r="J45" s="15" t="inlineStr">
         <is>
-          <t>เลขบัญชีผู้รับ</t>
+          <t>สาขา</t>
         </is>
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>Receiving bank account number.</t>
+          <t>Receiving bank branch.</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3878,12 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankAccountName</t>
+          <t>ReceivingBankAccountNumber</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>ReceivingBankAccountName</t>
+          <t>ReceivingBankAccountNumber</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -3500,12 +3910,12 @@
       <c r="I46" s="14" t="inlineStr"/>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>ชื่อบัญชีผู้รับ</t>
+          <t>เลขบัญชีผู้รับ</t>
         </is>
       </c>
       <c r="K46" s="16" t="inlineStr">
         <is>
-          <t>Receiving account name.</t>
+          <t>Receiving bank account number.</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3925,12 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>TransferSecuritiesToAccount</t>
+          <t>ReceivingBankAccountName</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>TransferSecuritiesToAccount</t>
+          <t>ReceivingBankAccountName</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -3547,12 +3957,12 @@
       <c r="I47" s="14" t="inlineStr"/>
       <c r="J47" s="15" t="inlineStr">
         <is>
-          <t>โอนหลักทรัพย์ไปบัญชี</t>
+          <t>ชื่อบัญชีผู้รับ</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr">
         <is>
-          <t>Target account for securities transfer.</t>
+          <t>Receiving account name.</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3972,12 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>TransferSecuritiesToBroker</t>
+          <t>TransferSecuritiesToAccount</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>TransferSecuritiesToBroker</t>
+          <t>TransferSecuritiesToAccount</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -3594,59 +4004,59 @@
       <c r="I48" s="14" t="inlineStr"/>
       <c r="J48" s="15" t="inlineStr">
         <is>
+          <t>โอนหลักทรัพย์ไปบัญชี</t>
+        </is>
+      </c>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>Target account for securities transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>TransferSecuritiesToBroker</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>TransferSecuritiesToBroker</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Single line of text</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="14" t="inlineStr"/>
+      <c r="J49" s="15" t="inlineStr">
+        <is>
           <t>โอนไปโบรกเกอร์</t>
         </is>
       </c>
-      <c r="K48" s="16" t="inlineStr">
+      <c r="K49" s="16" t="inlineStr">
         <is>
           <t>Target broker for securities transfer.  •  B2B: broker fees deducted from FCY first</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>TotalBalance</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>TotalBalance</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" s="20" t="inlineStr"/>
-      <c r="I49" s="21" t="inlineStr"/>
-      <c r="J49" s="22" t="inlineStr">
-        <is>
-          <t>ยอดเงินรวม (Wallet App)</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="inlineStr">
-        <is>
-          <t>Total balance keyed by Middle in Precheck Wallet App.  •  Middle-1 → shown on the Wallet precheck card</t>
         </is>
       </c>
     </row>
@@ -3656,17 +4066,17 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>IdentityCISVerified</t>
+          <t>TotalBalance</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>IdentityCISVerified</t>
+          <t>TotalBalance</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>Single line of text</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
@@ -3688,12 +4098,12 @@
       <c r="I50" s="21" t="inlineStr"/>
       <c r="J50" s="22" t="inlineStr">
         <is>
-          <t>ยืนยันตัวตน CIS (auto)</t>
+          <t>ยอดเงินรวม (Wallet App)</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>Auto-collected identity-verification status shown read-only (→ var gblIdentityCIS).  •  CAM-2; read-only label</t>
+          <t>Total balance keyed by Middle in Precheck Wallet App.  •  Middle-1 → shown on the Wallet precheck card</t>
         </is>
       </c>
     </row>
@@ -3703,17 +4113,17 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>AccruedInterestPosted</t>
+          <t>IdentityCISVerified</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>AccruedInterestPosted</t>
+          <t>IdentityCISVerified</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Single line of text</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
@@ -3735,12 +4145,12 @@
       <c r="I51" s="21" t="inlineStr"/>
       <c r="J51" s="22" t="inlineStr">
         <is>
-          <t>ดอกเบี้ยค้างรับที่ Post</t>
+          <t>ยืนยันตัวตน CIS (auto)</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>Accrued interest posted by C&amp;AM.  •  CAM-2</t>
+          <t>Auto-collected identity-verification status shown read-only (→ var gblIdentityCIS).  •  CAM-2; read-only label</t>
         </is>
       </c>
     </row>
@@ -3750,12 +4160,12 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>NetBalanceFinal</t>
+          <t>AccruedInterestPosted</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>NetBalanceFinal</t>
+          <t>AccruedInterestPosted</t>
         </is>
       </c>
       <c r="D52" s="19" t="inlineStr">
@@ -3782,59 +4192,59 @@
       <c r="I52" s="21" t="inlineStr"/>
       <c r="J52" s="22" t="inlineStr">
         <is>
+          <t>ดอกเบี้ยค้างรับที่ Post</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr">
+        <is>
+          <t>Accrued interest posted by C&amp;AM.  •  CAM-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>NetBalanceFinal</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>NetBalanceFinal</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr"/>
+      <c r="I53" s="21" t="inlineStr"/>
+      <c r="J53" s="22" t="inlineStr">
+        <is>
           <t>ยอดเงินสุทธิสุดท้าย</t>
         </is>
       </c>
-      <c r="K52" s="23" t="inlineStr">
+      <c r="K53" s="23" t="inlineStr">
         <is>
           <t>Final net balance before closing.  •  CAM-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>SalesRepresentative</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>SalesRepresentative</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Person or Group</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G53" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr"/>
-      <c r="I53" s="14" t="inlineStr"/>
-      <c r="J53" s="15" t="inlineStr">
-        <is>
-          <t>เจ้าหน้าที่ Sales</t>
-        </is>
-      </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>Sales owner of the request.</t>
         </is>
       </c>
     </row>
@@ -3844,17 +4254,17 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>InvestmentConsultantCode</t>
+          <t>SalesRepresentative</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>InvestmentConsultantCode</t>
+          <t>SalesRepresentative</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Single line of text</t>
+          <t>Person or Group</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -3876,263 +4286,259 @@
       <c r="I54" s="14" t="inlineStr"/>
       <c r="J54" s="15" t="inlineStr">
         <is>
+          <t>เจ้าหน้าที่ Sales</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t>Sales owner of the request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>InvestmentConsultantCode</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>InvestmentConsultantCode</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Single line of text</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="inlineStr"/>
+      <c r="I55" s="14" t="inlineStr"/>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
           <t>รหัส IC</t>
         </is>
       </c>
-      <c r="K54" s="16" t="inlineStr">
+      <c r="K55" s="16" t="inlineStr">
         <is>
           <t>Investment consultant code.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>Choice</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr"/>
-      <c r="I55" s="21" t="inlineStr">
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr"/>
+      <c r="I56" s="21" t="inlineStr">
         <is>
           <t>Branch, eBiz</t>
         </is>
       </c>
-      <c r="J55" s="22" t="inlineStr">
+      <c r="J56" s="22" t="inlineStr">
         <is>
           <t>ช่องทาง</t>
         </is>
       </c>
-      <c r="K55" s="23" t="inlineStr">
+      <c r="K56" s="23" t="inlineStr">
         <is>
           <t>Where the request came from.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>RequestStatus</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>RequestStatus</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>Choice</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr"/>
-      <c r="I56" s="14" t="inlineStr">
+      <c r="H57" s="13" t="inlineStr"/>
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Draft, PrecheckInProgress, PendingDocuments, PendingApproval, Approved, InSettlement, InCashMgmt, Closing, Completed, Rejected</t>
         </is>
       </c>
-      <c r="J56" s="15" t="inlineStr">
+      <c r="J57" s="15" t="inlineStr">
         <is>
           <t>สถานะคำขอ</t>
         </is>
       </c>
-      <c r="K56" s="16" t="inlineStr">
+      <c r="K57" s="16" t="inlineStr">
         <is>
           <t>Workflow status.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="B57" s="18" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
         <is>
           <t>CurrentStage</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>CurrentStage</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Choice</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G57" s="25" t="inlineStr">
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H57" s="20" t="inlineStr"/>
-      <c r="I57" s="21" t="inlineStr">
+      <c r="H58" s="20" t="inlineStr"/>
+      <c r="I58" s="21" t="inlineStr">
         <is>
           <t>Sales, Precheck, MiddleVerify, HeadOfSales, CAM, Settlement, Cash, Completed</t>
         </is>
       </c>
-      <c r="J57" s="22" t="inlineStr">
+      <c r="J58" s="22" t="inlineStr">
         <is>
           <t>ขั้นตอนปัจจุบัน</t>
         </is>
       </c>
-      <c r="K57" s="23" t="inlineStr">
+      <c r="K58" s="23" t="inlineStr">
         <is>
           <t>Stage on the tracking rail (1–8).</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>CurrentAssignee</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>CurrentAssignee</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Person or Group</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr"/>
-      <c r="I58" s="14" t="inlineStr"/>
-      <c r="J58" s="15" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr"/>
+      <c r="I59" s="14" t="inlineStr"/>
+      <c r="J59" s="15" t="inlineStr">
         <is>
           <t>ผู้รับผิดชอบปัจจุบัน</t>
         </is>
       </c>
-      <c r="K58" s="16" t="inlineStr">
+      <c r="K59" s="16" t="inlineStr">
         <is>
           <t>Who must act next.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="B59" s="18" t="inlineStr">
-        <is>
-          <t>IsLocked</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>IsLocked</t>
-        </is>
-      </c>
-      <c r="D59" s="19" t="inlineStr">
-        <is>
-          <t>Yes/No</t>
-        </is>
-      </c>
-      <c r="E59" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H59" s="20" t="inlineStr"/>
-      <c r="I59" s="21" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
-        </is>
-      </c>
-      <c r="J59" s="22" t="inlineStr">
-        <is>
-          <t>บัญชีติด Lock</t>
-        </is>
-      </c>
-      <c r="K59" s="23" t="inlineStr">
-        <is>
-          <t>Any account lock found by C&amp;AM?  •  ติด Lock → Reject กลับ Middle</t>
         </is>
       </c>
     </row>
@@ -4142,17 +4548,17 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>LockType</t>
+          <t>IsLocked</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>LockType</t>
+          <t>IsLocked</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>Choice</t>
+          <t>Yes/No</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
@@ -4173,17 +4579,17 @@
       <c r="H60" s="20" t="inlineStr"/>
       <c r="I60" s="21" t="inlineStr">
         <is>
-          <t>Lock Offshore, Others Lock, No Lock</t>
+          <t>Yes / No</t>
         </is>
       </c>
       <c r="J60" s="22" t="inlineStr">
         <is>
-          <t>ประเภท Lock</t>
+          <t>บัญชีติด Lock</t>
         </is>
       </c>
       <c r="K60" s="23" t="inlineStr">
         <is>
-          <t>Which lock.</t>
+          <t>Any account lock found by C&amp;AM?  •  ติด Lock → Reject กลับ Middle</t>
         </is>
       </c>
     </row>
@@ -4193,17 +4599,17 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>iTradeFlag</t>
+          <t>LockType</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>iTradeFlag</t>
+          <t>LockType</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>Choice</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -4224,111 +4630,115 @@
       <c r="H61" s="20" t="inlineStr"/>
       <c r="I61" s="21" t="inlineStr">
         <is>
+          <t>Lock Offshore, Others Lock, No Lock</t>
+        </is>
+      </c>
+      <c r="J61" s="22" t="inlineStr">
+        <is>
+          <t>ประเภท Lock</t>
+        </is>
+      </c>
+      <c r="K61" s="23" t="inlineStr">
+        <is>
+          <t>Which lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>iTradeFlag</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>iTradeFlag</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H62" s="20" t="inlineStr"/>
+      <c r="I62" s="21" t="inlineStr">
+        <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="J61" s="22" t="inlineStr">
+      <c r="J62" s="22" t="inlineStr">
         <is>
           <t>iTrade Flag</t>
         </is>
       </c>
-      <c r="K61" s="23" t="inlineStr">
-        <is>
-          <t>iTrade flag found by Product Op EQ.  •  มี = ต้องปิดก่อนบน SBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="K62" s="23" t="inlineStr">
+        <is>
+          <t>iTrade flag — now checked by C&amp;AM at the Gate (moved out of Product Op EQ pre-check).  •  มี = ต้องปิดก่อนบน SBA; CAM Gate; round-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>ApproverRemarks</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>ApproverRemarks</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Multiple lines of text</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr"/>
-      <c r="I62" s="14" t="inlineStr"/>
-      <c r="J62" s="15" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr"/>
+      <c r="I63" s="14" t="inlineStr"/>
+      <c r="J63" s="15" t="inlineStr">
         <is>
           <t>ความเห็นผู้อนุมัติ</t>
         </is>
       </c>
-      <c r="K62" s="16" t="inlineStr">
+      <c r="K63" s="16" t="inlineStr">
         <is>
           <t>Remarks from approval stages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="17" t="n">
-        <v>58</v>
-      </c>
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>CCRecipients</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>CCRecipients</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>Single line of text</t>
-        </is>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr"/>
-      <c r="I63" s="21" t="inlineStr"/>
-      <c r="J63" s="22" t="inlineStr">
-        <is>
-          <t>ผู้รับสำเนา (CC)</t>
-        </is>
-      </c>
-      <c r="K63" s="23" t="inlineStr">
-        <is>
-          <t>Extra CC e-mails for the stage-completion mail (comma-separated).  •  อีเมลอัตโนมัติ box (Sales-1/2, Middle-2) → Flow 6</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4748,17 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>AlgoPrecheckStatus</t>
+          <t>CCRecipients</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>AlgoPrecheckStatus</t>
+          <t>CCRecipients</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>Choice</t>
+          <t>Single line of text</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
@@ -4367,19 +4777,15 @@
         </is>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
-      <c r="I64" s="21" t="inlineStr">
-        <is>
-          <t>ดำเนินการแล้ว, ยังไม่ดำเนินการ</t>
-        </is>
-      </c>
+      <c r="I64" s="21" t="inlineStr"/>
       <c r="J64" s="22" t="inlineStr">
         <is>
-          <t>Pre-check Algo</t>
+          <t>ผู้รับสำเนา (CC)</t>
         </is>
       </c>
       <c r="K64" s="23" t="inlineStr">
         <is>
-          <t>Stop model ที่ Jaeger — done or not.  •  CAM-1</t>
+          <t>Extra CC e-mails for the stage-completion mail (comma-separated).  •  อีเมลอัตโนมัติ box (Sales-1/2, Middle-2) → Flow 6</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4795,12 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>TFEXOffshoreApplicable</t>
+          <t>PostInterest</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TFEXOffshoreApplicable</t>
+          <t>PostInterest</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -4425,12 +4831,12 @@
       </c>
       <c r="J65" s="22" t="inlineStr">
         <is>
-          <t>มี TFEX / Offshore</t>
+          <t>Post ดอกเบี้ย?</t>
         </is>
       </c>
       <c r="K65" s="23" t="inlineStr">
         <is>
-          <t>Forced-order rule applies (TFEX withdraw-first / Offshore transfer-first).  •  Settlement screen</t>
+          <t>Cash Management decides whether to post accrued interest; No → skip the C&amp;AM post-interest step and close directly.  •  Cash Management queue; round-17</t>
         </is>
       </c>
     </row>
@@ -4440,17 +4846,17 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>RejectCount</t>
+          <t>SettlementDispatchedAt</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>RejectCount</t>
+          <t>SettlementDispatchedAt</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Date and Time</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -4472,10 +4878,108 @@
       <c r="I66" s="21" t="inlineStr"/>
       <c r="J66" s="22" t="inlineStr">
         <is>
+          <t>เวลา Dispatch งาน</t>
+        </is>
+      </c>
+      <c r="K66" s="23" t="inlineStr">
+        <is>
+          <t>When the C&amp;AM Gate dispatched the parallel settlement tasks (Flow 7).  •  round-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>TFEXOffshoreApplicable</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>TFEXOffshoreApplicable</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" s="20" t="inlineStr"/>
+      <c r="I67" s="21" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
+        </is>
+      </c>
+      <c r="J67" s="22" t="inlineStr">
+        <is>
+          <t>มี TFEX / Offshore</t>
+        </is>
+      </c>
+      <c r="K67" s="23" t="inlineStr">
+        <is>
+          <t>Forced-order rule applies (TFEX withdraw-first / Offshore transfer-first).  •  Settlement screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>RejectCount</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>RejectCount</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr"/>
+      <c r="I68" s="21" t="inlineStr"/>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
           <t>จำนวนครั้งที่ถูก Reject</t>
         </is>
       </c>
-      <c r="K66" s="23" t="inlineStr">
+      <c r="K68" s="23" t="inlineStr">
         <is>
           <t>Denormalized reject counter shown on the Dashboard list.  •  Flow 3 increments on Reject — avoids counting Approval_Logs per row (fast, delegable)</t>
         </is>
@@ -4498,7 +5002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4879,53 +5383,53 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>HasNoAssets</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>HasNoAssets</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Yes/No</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>ไม่มีทรัพย์สินคงเหลือ</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>Matrix column 1.  •  วาดจาก varColAssets / ติ๊กรายบัญชี</t>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>AssetMoneyState</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>AssetMoneyState</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>NoAssets (ไม่มีทรัพย์สินคงเหลือ), NoMoney (ไม่มีเงินคงเหลือ), MoneyUnknown (มีเงินแต่ไม่ทราบยอด)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>สถานะทรัพย์สิน/เงิน</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Single-select per account (round-17 matrix): checking one clears the others in that row.</t>
         </is>
       </c>
     </row>
@@ -4935,17 +5439,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>HasNoMoney</t>
+          <t>ToggleValue</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HasNoMoney</t>
+          <t>ToggleValue</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>Single line of text</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -4964,19 +5468,15 @@
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
-        </is>
-      </c>
+      <c r="I13" s="14" t="inlineStr"/>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>ไม่มีเงินคงเหลือ</t>
+          <t>ค่า มี/ไม่มี</t>
         </is>
       </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
-          <t>Matrix column 2.</t>
+          <t>SAXO / GTN toggle value.  •  มี, ไม่มี</t>
         </is>
       </c>
     </row>
@@ -4986,17 +5486,17 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>HasMoneyUnknownAmount</t>
+          <t>EditedBy</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>HasMoneyUnknownAmount</t>
+          <t>EditedBy</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>Person or Group</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -5015,256 +5515,60 @@
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
-        </is>
-      </c>
+      <c r="I14" s="14" t="inlineStr"/>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>มีเงิน แต่ไม่ทราบยอดสุทธิ</t>
+          <t>แก้ไขโดย</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
         <is>
-          <t>Matrix column 3.</t>
+          <t>Last editor (the ⟲ attribution line).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>HasUnitHolder</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>HasUnitHolder</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Yes/No</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
-        <is>
-          <t>มี unit holder account</t>
-        </is>
-      </c>
-      <c r="K15" s="23" t="inlineStr">
-        <is>
-          <t>The unit-holder checkbox in the fund group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>UnitHolderAccounts</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>UnitHolderAccounts</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Single line of text</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>บัญชี unit holder</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>Comma-separated unit-holder accounts (fund group).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>ToggleValue</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>ToggleValue</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Single line of text</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>ค่า มี/ไม่มี</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>SAXO / GTN toggle value.  •  มี, ไม่มี</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>EditedBy</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>EditedBy</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Person or Group</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>แก้ไขโดย</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>Last editor (the ⟲ attribution line).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>EditedAt</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>EditedAt</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Date and Time</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr"/>
-      <c r="I19" s="14" t="inlineStr"/>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr"/>
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>แก้ไขเมื่อ</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t>Last edit timestamp.</t>
         </is>
@@ -5287,7 +5591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5306,14 +5610,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Request_Tasks   ·   งานปิดบัญชี (1 งาน = 1 แถว)</t>
+          <t>Request_Tasks   ·   งานปิดบัญชี (1 งาน = 1 แถว) · Settlement engine</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Type: List (new)    ·    Child — one row per closing task. Feeds every portfolio / closing-task table (Middle-2, CAM-2/3, Settlement, Cash, EQ-2, Offshore).</t>
+          <t>Type: List (new)    ·    Child — one row per closing task; the SETTLEMENT TASK ENGINE spine (round-17). Rows are expanded from Task_Templates for each product the customer holds; each department's queue = Filter(RequestID, Status=Ready, ResponsibleTeam=self). Completing a task unlocks the next StepNo of the same product.</t>
         </is>
       </c>
     </row>
@@ -5476,100 +5780,100 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>AccountGroup</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>AccountGroup</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Single line of text</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr"/>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>กลุ่มบัญชี</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>TFEX / Offshore / Equity+Bond+SN / …  •  Group header rows in the table</t>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>TFEX, Offshore, Equity + Bond + SN, บัญชีซื้อขายหน่วยลงทุน, DA Digital Assets, LiVEx, Algo</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Which product chain this task belongs to (round-17 engine).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>ResponsibleTeam</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>ResponsibleTeam</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Choice</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Cash Management, Client &amp; Account Mgmt, product operation - EQ, product operation - Offshore, DA Team</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>ทีมที่รับผิดชอบ</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>Owner team of the task.</t>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>StepNo</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>StepNo</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>ลำดับขั้น</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>Order within the product chain; a step is Ready only when the previous step is Done.  •  round-17 engine</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5883,12 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>TaskName</t>
+          <t>AccountGroup</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>TaskName</t>
+          <t>AccountGroup</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -5611,12 +5915,12 @@
       <c r="I10" s="14" t="inlineStr"/>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>งานที่ต้องทำ</t>
+          <t>กลุ่มบัญชี</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr">
         <is>
-          <t>e.g. เช็ค Position, ถอน+โอนเงิน THB.</t>
+          <t>Account group label for display.  •  Group header rows</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5930,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>ResponsibleTeam</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>ResponsibleTeam</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -5657,17 +5961,17 @@
       <c r="H11" s="13" t="inlineStr"/>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>รอทำ, เสร็จแล้ว</t>
+          <t>CAM, Cash, EQ, Offshore, DA</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>สถานะ</t>
+          <t>ทีมที่รับผิดชอบ</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr">
         <is>
-          <t>Task status pill.</t>
+          <t>Owning department; drives which queue the task appears in.</t>
         </is>
       </c>
     </row>
@@ -5677,17 +5981,17 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>IsExempt</t>
+          <t>TaskName</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>IsExempt</t>
+          <t>TaskName</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>Single line of text</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -5705,71 +6009,67 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
-        </is>
-      </c>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>ไม่บังคับ</t>
+          <t>งานที่ต้องทำ</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>Optional rows (withdrawals; DA non-suspend).</t>
+          <t>e.g. เช็ค Position, ถอน+โอนเงิน THB.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>DoneBy</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>DoneBy</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Person or Group</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>ทำโดย</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>Who completed it (ทำโดย column).</t>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>Locked, Ready, Done, Skipped, Rejected</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>สถานะ</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>Task lifecycle (round-17): Locked→Ready→Done; Skipped for passed-optional; Rejected on terminal reject.</t>
         </is>
       </c>
     </row>
@@ -5779,42 +6079,144 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
+          <t>IsExempt</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>IsExempt</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>ไม่บังคับ</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>Optional rows (Offshore FCD; DA transfer-if-alive; post-interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>DoneBy</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>DoneBy</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Person or Group</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr"/>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>ทำโดย</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>Who completed it (ทำโดย column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
           <t>DoneAt</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>DoneAt</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Date and Time</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr"/>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>ทำเมื่อ</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K16" s="16" t="inlineStr">
         <is>
           <t>Completion timestamp.</t>
         </is>
@@ -5856,14 +6258,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Request_Prechecks   ·   ผล pre-check 3 ทีม (1 ทีม = 1 แถว)</t>
+          <t>Request_Prechecks   ·   ผล pre-check 2 ทีม (1 ทีม = 1 แถว)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Type: List (new)    ·    Child — exactly 3 rows per request (DA / Middle / EQ). Feeds the parallel pre-check cards and the routing gate (Flow 4).</t>
+          <t>Type: List (new)    ·    Child — exactly 2 rows per request (DA / Middle) in round-17. Feeds the parallel pre-check cards and the routing gate (Flow 4). Product Op EQ removed from pre-check (its iTrade check moved to the C&amp;AM Gate).</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6464,7 @@
       <c r="H8" s="13" t="inlineStr"/>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>DigitalAssets, Middle, ProductOpEQ</t>
+          <t>DigitalAssets, Middle</t>
         </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
@@ -6072,7 +6474,7 @@
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>Which parallel team.</t>
+          <t>Which parallel pre-check team (round-17: 2 teams only).</t>
         </is>
       </c>
     </row>
